--- a/data/Tablas de mortalidad 2010,2019 y 2021.xlsx
+++ b/data/Tablas de mortalidad 2010,2019 y 2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Documents\DEMOGRAFÍA\DEMOGRAPHY_9219\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B2AEC-5AD8-4809-A7D5-F849BF146D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0FF624-9779-4D20-B126-62F6A6DAA4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{651F2614-5642-439D-A7D3-7C598B0D877E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{651F2614-5642-439D-A7D3-7C598B0D877E}"/>
   </bookViews>
   <sheets>
     <sheet name="Mortalidad femenina 2010" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Mortalidad femenina 2021" sheetId="6" r:id="rId5"/>
     <sheet name="Mortalidad masculina 2021" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="1000" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,8 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
